--- a/data/customers.xlsx
+++ b/data/customers.xlsx
@@ -6,13 +6,13 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers" r:id="rId3" sheetId="1"/>
+    <sheet name="Data Gabungan" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>Nama</t>
   </si>
@@ -21,6 +21,36 @@
   </si>
   <si>
     <t>Alamat</t>
+  </si>
+  <si>
+    <t>Plat Nomor</t>
+  </si>
+  <si>
+    <t>Merk</t>
+  </si>
+  <si>
+    <t>Tipe</t>
+  </si>
+  <si>
+    <t>Tahun</t>
+  </si>
+  <si>
+    <t>bayu</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>malang</t>
+  </si>
+  <si>
+    <t>nmax</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>2024</t>
   </si>
 </sst>
 </file>
@@ -65,7 +95,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -78,6 +108,41 @@
       <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
+      <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/data/customers.xlsx
+++ b/data/customers.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="140">
   <si>
     <t>Nama</t>
   </si>
@@ -430,6 +430,9 @@
   </si>
   <si>
     <t>82190876543</t>
+  </si>
+  <si>
+    <t>2023</t>
   </si>
 </sst>
 </file>
@@ -727,8 +730,8 @@
       <c r="F2" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="G2" t="n" s="0">
-        <v>2023.0</v>
+      <c r="G2" t="s" s="0">
+        <v>139</v>
       </c>
     </row>
     <row r="3">

--- a/data/customers.xlsx
+++ b/data/customers.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="146">
   <si>
     <t>Nama</t>
   </si>
@@ -433,6 +433,24 @@
   </si>
   <si>
     <t>2023</t>
+  </si>
+  <si>
+    <t>Bayu Adi Nugroho</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>Mojokerto</t>
+  </si>
+  <si>
+    <t>B 4 Y U</t>
+  </si>
+  <si>
+    <t>Amfibi</t>
+  </si>
+  <si>
+    <t>2050</t>
   </si>
 </sst>
 </file>
@@ -685,7 +703,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
@@ -1401,6 +1419,29 @@
         <v>2024.0</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
